--- a/artfynd/A 11238-2026 artfynd.xlsx
+++ b/artfynd/A 11238-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131914677</v>
+        <v>131914919</v>
       </c>
       <c r="B2" t="n">
-        <v>101323</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469478</v>
+        <v>469350</v>
       </c>
       <c r="R2" t="n">
-        <v>7013162</v>
+        <v>7013316</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131914631</v>
+        <v>131914847</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödön, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469527</v>
+        <v>469368</v>
       </c>
       <c r="R3" t="n">
-        <v>7013077</v>
+        <v>7013307</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131914261</v>
+        <v>131914412</v>
       </c>
       <c r="B4" t="n">
-        <v>101323</v>
+        <v>96410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469718</v>
+        <v>469661</v>
       </c>
       <c r="R4" t="n">
-        <v>7013185</v>
+        <v>7013115</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket rikligt i markskiktet i området</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,50 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131915166</v>
+        <v>131947472</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>96410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödön, Rödön, Jmt</t>
+          <t>Rödögården, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469609</v>
+        <v>469444</v>
       </c>
       <c r="R5" t="n">
-        <v>7013242</v>
+        <v>7013212</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,24 +1069,9 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på flertalet granar utmed vägen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,57 +1086,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131914847</v>
+        <v>131947477</v>
       </c>
       <c r="B6" t="n">
-        <v>91908</v>
+        <v>96410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rödön, Rödön, Jmt</t>
+          <t>Rödögården, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469368</v>
+        <v>469614</v>
       </c>
       <c r="R6" t="n">
-        <v>7013307</v>
+        <v>7013029</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,19 +1166,9 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,65 +1183,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131914644</v>
+        <v>131914765</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>92199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödön, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469554</v>
+        <v>469401</v>
       </c>
       <c r="R7" t="n">
-        <v>7013075</v>
+        <v>7013218</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1265,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,12 +1275,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131914692</v>
+        <v>131947480</v>
       </c>
       <c r="B8" t="n">
-        <v>92868</v>
+        <v>92199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,34 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödön, Rödön, Jmt</t>
+          <t>Rödögården, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469465</v>
+        <v>469375</v>
       </c>
       <c r="R8" t="n">
-        <v>7013147</v>
+        <v>7013184</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,19 +1370,9 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,69 +1387,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131914476</v>
+        <v>131947484</v>
       </c>
       <c r="B9" t="n">
-        <v>58114</v>
+        <v>92199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rödön, Rödön, Jmt</t>
+          <t>Rödögården, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469617</v>
+        <v>469402</v>
       </c>
       <c r="R9" t="n">
-        <v>7013081</v>
+        <v>7013214</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,19 +1467,9 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,44 +1484,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131914919</v>
+        <v>131914469</v>
       </c>
       <c r="B10" t="n">
-        <v>91904</v>
+        <v>92943</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1605,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469350</v>
+        <v>469643</v>
       </c>
       <c r="R10" t="n">
-        <v>7013316</v>
+        <v>7013046</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,7 +1566,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,14 +1576,19 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkroppar. Mest sannolikt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1677,57 +1608,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131914658</v>
+        <v>131914692</v>
       </c>
       <c r="B11" t="n">
-        <v>58114</v>
+        <v>92943</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödön, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469562</v>
+        <v>469465</v>
       </c>
       <c r="R11" t="n">
-        <v>7013082</v>
+        <v>7013147</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1678,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,12 +1688,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spelande</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,50 +1715,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131914889</v>
+        <v>131947475</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>80493</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödön, Rödön, Jmt</t>
+          <t>Rödögården, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469365</v>
+        <v>469613</v>
       </c>
       <c r="R12" t="n">
-        <v>7013325</v>
+        <v>7013078</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,24 +1783,9 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Barkfläkt klen gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,60 +1800,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131914765</v>
+        <v>131914631</v>
       </c>
       <c r="B13" t="n">
-        <v>92631</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödön, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469401</v>
+        <v>469527</v>
       </c>
       <c r="R13" t="n">
-        <v>7013218</v>
+        <v>7013077</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,7 +1887,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,7 +1897,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,45 +1929,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131947480</v>
+        <v>131914644</v>
       </c>
       <c r="B14" t="n">
-        <v>92632</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rödögården, Jmt</t>
+          <t>Rödön, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469375</v>
+        <v>469554</v>
       </c>
       <c r="R14" t="n">
-        <v>7013184</v>
+        <v>7013075</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,9 +2002,24 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,22 +2034,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131947481</v>
+        <v>131914889</v>
       </c>
       <c r="B15" t="n">
-        <v>58114</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,46 +2057,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rödögården, Jmt</t>
+          <t>Rödön, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469446</v>
+        <v>469365</v>
       </c>
       <c r="R15" t="n">
-        <v>7013308</v>
+        <v>7013325</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2199,9 +2119,24 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Barkfläkt klen gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2216,57 +2151,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131947484</v>
+        <v>131915083</v>
       </c>
       <c r="B16" t="n">
-        <v>92632</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rödögården, Jmt</t>
+          <t>Rödön, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469402</v>
+        <v>469500</v>
       </c>
       <c r="R16" t="n">
-        <v>7013214</v>
+        <v>7013355</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,9 +2236,24 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,57 +2268,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131947478</v>
+        <v>131915166</v>
       </c>
       <c r="B17" t="n">
-        <v>101325</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rödögården, Jmt</t>
+          <t>Rödön, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469443</v>
+        <v>469609</v>
       </c>
       <c r="R17" t="n">
-        <v>7013211</v>
+        <v>7013242</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,9 +2353,24 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på flertalet granar utmed vägen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,12 +2385,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2425,7 +2400,7 @@
         <v>131947479</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2540,48 +2515,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131947475</v>
+        <v>131914476</v>
       </c>
       <c r="B19" t="n">
-        <v>80461</v>
+        <v>58136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rödögården, Jmt</t>
+          <t>Rödön, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469613</v>
+        <v>469617</v>
       </c>
       <c r="R19" t="n">
-        <v>7013078</v>
+        <v>7013081</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,9 +2592,19 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,15 +2619,988 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131914658</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rödön, Rödön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>469562</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7013082</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spelande</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131915184</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rödön, Rödön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>469726</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7013309</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131947481</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rödögården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>469446</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7013308</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Maria Danvind</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Maria Danvind</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131914276</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rödön, Rödön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>469677</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7013161</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131914261</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rödön, Rödön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>469718</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7013185</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131914344</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rödön, Rödön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>469686</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7013104</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131914677</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rödön, Rödön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>469478</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7013162</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131947473</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Rödögården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>469614</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7013029</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131947478</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Rödögården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>469443</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7013211</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11238-2026 artfynd.xlsx
+++ b/artfynd/A 11238-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914919</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914847</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914412</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947472</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947477</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914765</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947480</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947484</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914469</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914692</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947475</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914631</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2043,6 +2108,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914644</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914889</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131915083</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2394,6 +2474,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131915166</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2512,6 +2597,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947479</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2628,6 +2718,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914476</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2749,6 +2844,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914658</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2865,6 +2965,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131915184</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2974,6 +3079,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947481</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3086,6 +3196,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914276</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3193,6 +3308,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914261</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3300,6 +3420,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914344</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3407,6 +3532,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914677</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3504,6 +3634,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947473</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3601,8 +3736,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947478</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>